--- a/docs/StructureDefinition-LabObservationElectronMicroscopy.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
